--- a/Bibsam_tidskriftslistor/scifree_data_acs.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_acs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_0A85699B7AAE7F5D9773BBB70C04666ADBADB3B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{255D78B7-8803-4691-B60D-A633E5D75F5C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BDFBE3-2DA4-4D7B-B36A-BF0F2CCA550C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="319">
   <si>
     <t>Open</t>
   </si>
@@ -950,6 +950,33 @@
   </si>
   <si>
     <t>https://pubs.acs.org/journal/pcrhej</t>
+  </si>
+  <si>
+    <t>3067-5928</t>
+  </si>
+  <si>
+    <t>ACS Nano Medicine</t>
+  </si>
+  <si>
+    <t>https://pubs.acs.org/journal/anmafm</t>
+  </si>
+  <si>
+    <t>3067-6037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACS Nutrition Science </t>
+  </si>
+  <si>
+    <t>https://pubs.acs.org/journal/ansadg</t>
+  </si>
+  <si>
+    <t>2998-8799</t>
+  </si>
+  <si>
+    <t>Photon Science</t>
+  </si>
+  <si>
+    <t>https://pubs.acs.org/journal/psabes</t>
   </si>
 </sst>
 </file>
@@ -1005,19 +1032,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C66BE705-1E5A-4303-AF83-D4C5F023D2E9}" name="Table1" displayName="Table1" ref="A1:G88" totalsRowShown="0">
-  <autoFilter ref="A1:G88" xr:uid="{C66BE705-1E5A-4303-AF83-D4C5F023D2E9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G88">
-    <sortCondition ref="D1:D88"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D0C33BAA-0CB8-487E-92B5-A3B6BE941941}" name="Table2" displayName="Table2" ref="A1:G91" totalsRowShown="0">
+  <autoFilter ref="A1:G91" xr:uid="{D0C33BAA-0CB8-487E-92B5-A3B6BE941941}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G91">
+    <sortCondition ref="D1:D91"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F238F233-0310-40EB-BA15-E60E17D8E5A6}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{7129BCA7-E91A-4A15-B341-0FBB36F2191B}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{9AAD0F0B-84CA-4CC3-98CB-544B5E37668D}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{266D219D-02EB-434C-BFC8-4D68D7647EF5}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{AA394E15-5997-4731-9B07-B12B68F4943C}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{0FA508A0-F1D3-4C86-B004-B0A75BFD5E6E}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{CA3158FD-D75E-484F-A761-921186AF69AB}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{EAA4833A-9A72-47FC-84DE-4E38012153D4}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{9A309FAF-C1B7-47B2-86E5-DD7BBBDE8CCF}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{EAC57E0F-DC1F-4F55-B448-47D1E8F202B3}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{7F7F88B3-BB4C-4D3B-8270-B66365DE63A6}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{6BE53B89-C57B-418A-8C5D-B6AC4ACDD11F}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{C41A1670-3EDF-414A-8DC0-BDA490651272}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{4B6BB711-4FF9-439B-8F3F-942B19308385}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1285,8 +1312,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F61CB2-64B3-4DEA-923F-CE31E41FE58A}">
-  <dimension ref="A1:G88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B195C7CE-1487-48C8-9ABA-A4981AAD76AA}">
+  <dimension ref="A1:G91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -2021,16 +2048,16 @@
         <v>162</v>
       </c>
       <c r="B36" t="s">
-        <v>271</v>
+        <v>310</v>
       </c>
       <c r="D36" t="s">
-        <v>241</v>
+        <v>311</v>
       </c>
       <c r="E36" t="s">
-        <v>242</v>
+        <v>312</v>
       </c>
       <c r="F36" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G36" t="s">
         <v>161</v>
@@ -2041,13 +2068,13 @@
         <v>162</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>271</v>
       </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>241</v>
       </c>
       <c r="E37" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="F37" t="s">
         <v>0</v>
@@ -2061,16 +2088,16 @@
         <v>162</v>
       </c>
       <c r="B38" t="s">
-        <v>238</v>
+        <v>313</v>
       </c>
       <c r="D38" t="s">
-        <v>239</v>
+        <v>314</v>
       </c>
       <c r="E38" t="s">
-        <v>240</v>
+        <v>315</v>
       </c>
       <c r="F38" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G38" t="s">
         <v>161</v>
@@ -2081,16 +2108,16 @@
         <v>162</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G39" t="s">
         <v>161</v>
@@ -2101,16 +2128,16 @@
         <v>162</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>238</v>
       </c>
       <c r="D40" t="s">
-        <v>55</v>
+        <v>239</v>
       </c>
       <c r="E40" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G40" t="s">
         <v>161</v>
@@ -2121,16 +2148,16 @@
         <v>162</v>
       </c>
       <c r="B41" t="s">
-        <v>270</v>
+        <v>52</v>
       </c>
       <c r="D41" t="s">
-        <v>236</v>
+        <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>237</v>
+        <v>183</v>
       </c>
       <c r="F41" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G41" t="s">
         <v>161</v>
@@ -2141,16 +2168,16 @@
         <v>162</v>
       </c>
       <c r="B42" t="s">
-        <v>269</v>
+        <v>54</v>
       </c>
       <c r="D42" t="s">
-        <v>234</v>
+        <v>55</v>
       </c>
       <c r="E42" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="F42" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G42" t="s">
         <v>161</v>
@@ -2161,16 +2188,16 @@
         <v>162</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>270</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>236</v>
       </c>
       <c r="E43" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G43" t="s">
         <v>161</v>
@@ -2181,16 +2208,16 @@
         <v>162</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>269</v>
       </c>
       <c r="D44" t="s">
-        <v>59</v>
+        <v>234</v>
       </c>
       <c r="E44" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G44" t="s">
         <v>161</v>
@@ -2201,13 +2228,13 @@
         <v>162</v>
       </c>
       <c r="B45" t="s">
-        <v>294</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>295</v>
+        <v>57</v>
       </c>
       <c r="E45" t="s">
-        <v>296</v>
+        <v>185</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
@@ -2221,13 +2248,13 @@
         <v>162</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
@@ -2241,16 +2268,13 @@
         <v>162</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" t="s">
-        <v>63</v>
+        <v>294</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>295</v>
       </c>
       <c r="E47" t="s">
-        <v>188</v>
+        <v>296</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
@@ -2264,16 +2288,16 @@
         <v>162</v>
       </c>
       <c r="B48" t="s">
-        <v>303</v>
+        <v>60</v>
       </c>
       <c r="D48" t="s">
-        <v>304</v>
+        <v>61</v>
       </c>
       <c r="E48" t="s">
-        <v>305</v>
+        <v>187</v>
       </c>
       <c r="F48" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G48" t="s">
         <v>161</v>
@@ -2284,16 +2308,16 @@
         <v>162</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D49" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
@@ -2307,19 +2331,16 @@
         <v>162</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" t="s">
-        <v>69</v>
+        <v>303</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>304</v>
       </c>
       <c r="E50" t="s">
-        <v>190</v>
+        <v>305</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G50" t="s">
         <v>161</v>
@@ -2330,16 +2351,16 @@
         <v>162</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C51" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F51" t="s">
         <v>11</v>
@@ -2353,16 +2374,19 @@
         <v>162</v>
       </c>
       <c r="B52" t="s">
-        <v>297</v>
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>69</v>
       </c>
       <c r="D52" t="s">
-        <v>298</v>
+        <v>70</v>
       </c>
       <c r="E52" t="s">
-        <v>299</v>
+        <v>190</v>
       </c>
       <c r="F52" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G52" t="s">
         <v>161</v>
@@ -2373,16 +2397,19 @@
         <v>162</v>
       </c>
       <c r="B53" t="s">
-        <v>277</v>
+        <v>71</v>
+      </c>
+      <c r="C53" t="s">
+        <v>72</v>
       </c>
       <c r="D53" t="s">
-        <v>287</v>
+        <v>73</v>
       </c>
       <c r="E53" t="s">
-        <v>283</v>
+        <v>191</v>
       </c>
       <c r="F53" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G53" t="s">
         <v>161</v>
@@ -2393,19 +2420,16 @@
         <v>162</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" t="s">
-        <v>75</v>
+        <v>297</v>
       </c>
       <c r="D54" t="s">
-        <v>76</v>
+        <v>298</v>
       </c>
       <c r="E54" t="s">
-        <v>192</v>
+        <v>299</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G54" t="s">
         <v>161</v>
@@ -2416,19 +2440,16 @@
         <v>162</v>
       </c>
       <c r="B55" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" t="s">
-        <v>78</v>
+        <v>277</v>
       </c>
       <c r="D55" t="s">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="E55" t="s">
-        <v>193</v>
+        <v>283</v>
       </c>
       <c r="F55" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G55" t="s">
         <v>161</v>
@@ -2439,16 +2460,16 @@
         <v>162</v>
       </c>
       <c r="B56" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D56" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E56" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s">
         <v>11</v>
@@ -2462,16 +2483,16 @@
         <v>162</v>
       </c>
       <c r="B57" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D57" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E57" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F57" t="s">
         <v>11</v>
@@ -2485,16 +2506,16 @@
         <v>162</v>
       </c>
       <c r="B58" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E58" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F58" t="s">
         <v>11</v>
@@ -2508,16 +2529,19 @@
         <v>162</v>
       </c>
       <c r="B59" t="s">
-        <v>278</v>
+        <v>83</v>
+      </c>
+      <c r="C59" t="s">
+        <v>84</v>
       </c>
       <c r="D59" t="s">
-        <v>288</v>
+        <v>85</v>
       </c>
       <c r="E59" t="s">
-        <v>284</v>
+        <v>195</v>
       </c>
       <c r="F59" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G59" t="s">
         <v>161</v>
@@ -2528,16 +2552,16 @@
         <v>162</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E60" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F60" t="s">
         <v>11</v>
@@ -2551,16 +2575,16 @@
         <v>162</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>278</v>
       </c>
       <c r="D61" t="s">
-        <v>93</v>
+        <v>288</v>
       </c>
       <c r="E61" t="s">
-        <v>198</v>
+        <v>284</v>
       </c>
       <c r="F61" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G61" t="s">
         <v>161</v>
@@ -2571,16 +2595,16 @@
         <v>162</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D62" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E62" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F62" t="s">
         <v>11</v>
@@ -2594,16 +2618,13 @@
         <v>162</v>
       </c>
       <c r="B63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C63" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D63" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E63" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F63" t="s">
         <v>11</v>
@@ -2617,16 +2638,19 @@
         <v>162</v>
       </c>
       <c r="B64" t="s">
-        <v>263</v>
+        <v>94</v>
+      </c>
+      <c r="C64" t="s">
+        <v>95</v>
       </c>
       <c r="D64" t="s">
-        <v>252</v>
+        <v>96</v>
       </c>
       <c r="E64" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="F64" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
@@ -2637,16 +2661,16 @@
         <v>162</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D65" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E65" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F65" t="s">
         <v>11</v>
@@ -2660,19 +2684,16 @@
         <v>162</v>
       </c>
       <c r="B66" t="s">
-        <v>103</v>
-      </c>
-      <c r="C66" t="s">
-        <v>104</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>105</v>
+        <v>252</v>
       </c>
       <c r="E66" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="F66" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G66" t="s">
         <v>161</v>
@@ -2683,16 +2704,16 @@
         <v>162</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D67" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E67" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F67" t="s">
         <v>11</v>
@@ -2706,16 +2727,16 @@
         <v>162</v>
       </c>
       <c r="B68" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C68" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E68" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F68" t="s">
         <v>11</v>
@@ -2729,16 +2750,16 @@
         <v>162</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C69" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D69" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E69" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F69" t="s">
         <v>11</v>
@@ -2752,16 +2773,16 @@
         <v>162</v>
       </c>
       <c r="B70" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C70" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D70" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E70" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F70" t="s">
         <v>11</v>
@@ -2775,16 +2796,16 @@
         <v>162</v>
       </c>
       <c r="B71" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C71" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D71" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E71" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F71" t="s">
         <v>11</v>
@@ -2798,16 +2819,16 @@
         <v>162</v>
       </c>
       <c r="B72" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D72" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E72" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F72" t="s">
         <v>11</v>
@@ -2821,16 +2842,16 @@
         <v>162</v>
       </c>
       <c r="B73" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D73" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E73" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F73" t="s">
         <v>11</v>
@@ -2844,16 +2865,16 @@
         <v>162</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C74" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D74" t="s">
-        <v>273</v>
+        <v>123</v>
       </c>
       <c r="E74" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F74" t="s">
         <v>11</v>
@@ -2867,16 +2888,16 @@
         <v>162</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C75" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D75" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E75" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F75" t="s">
         <v>11</v>
@@ -2890,16 +2911,16 @@
         <v>162</v>
       </c>
       <c r="B76" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C76" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D76" t="s">
-        <v>134</v>
+        <v>273</v>
       </c>
       <c r="E76" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F76" t="s">
         <v>11</v>
@@ -2913,16 +2934,16 @@
         <v>162</v>
       </c>
       <c r="B77" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C77" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D77" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E77" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F77" t="s">
         <v>11</v>
@@ -2936,16 +2957,16 @@
         <v>162</v>
       </c>
       <c r="B78" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C78" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D78" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E78" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F78" t="s">
         <v>11</v>
@@ -2959,16 +2980,16 @@
         <v>162</v>
       </c>
       <c r="B79" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C79" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D79" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E79" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F79" t="s">
         <v>11</v>
@@ -2982,16 +3003,16 @@
         <v>162</v>
       </c>
       <c r="B80" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C80" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D80" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E80" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F80" t="s">
         <v>11</v>
@@ -3005,16 +3026,16 @@
         <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C81" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D81" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E81" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F81" t="s">
         <v>11</v>
@@ -3028,16 +3049,19 @@
         <v>162</v>
       </c>
       <c r="B82" t="s">
-        <v>306</v>
+        <v>144</v>
+      </c>
+      <c r="C82" t="s">
+        <v>145</v>
       </c>
       <c r="D82" t="s">
-        <v>307</v>
+        <v>146</v>
       </c>
       <c r="E82" t="s">
-        <v>308</v>
+        <v>216</v>
       </c>
       <c r="F82" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G82" t="s">
         <v>161</v>
@@ -3048,16 +3072,19 @@
         <v>162</v>
       </c>
       <c r="B83" t="s">
-        <v>279</v>
+        <v>147</v>
+      </c>
+      <c r="C83" t="s">
+        <v>148</v>
       </c>
       <c r="D83" t="s">
-        <v>289</v>
+        <v>149</v>
       </c>
       <c r="E83" t="s">
-        <v>309</v>
+        <v>217</v>
       </c>
       <c r="F83" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G83" t="s">
         <v>161</v>
@@ -3068,19 +3095,16 @@
         <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>150</v>
-      </c>
-      <c r="C84" t="s">
-        <v>151</v>
+        <v>316</v>
       </c>
       <c r="D84" t="s">
-        <v>152</v>
+        <v>317</v>
       </c>
       <c r="E84" t="s">
-        <v>218</v>
+        <v>318</v>
       </c>
       <c r="F84" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G84" t="s">
         <v>161</v>
@@ -3091,19 +3115,16 @@
         <v>162</v>
       </c>
       <c r="B85" t="s">
-        <v>153</v>
-      </c>
-      <c r="C85" t="s">
-        <v>154</v>
+        <v>306</v>
       </c>
       <c r="D85" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="E85" t="s">
-        <v>219</v>
+        <v>308</v>
       </c>
       <c r="F85" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G85" t="s">
         <v>161</v>
@@ -3114,19 +3135,16 @@
         <v>162</v>
       </c>
       <c r="B86" t="s">
-        <v>155</v>
-      </c>
-      <c r="C86" t="s">
-        <v>156</v>
+        <v>279</v>
       </c>
       <c r="D86" t="s">
-        <v>224</v>
+        <v>289</v>
       </c>
       <c r="E86" t="s">
-        <v>220</v>
+        <v>309</v>
       </c>
       <c r="F86" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G86" t="s">
         <v>161</v>
@@ -3137,16 +3155,16 @@
         <v>162</v>
       </c>
       <c r="B87" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C87" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D87" t="s">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="E87" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F87" t="s">
         <v>11</v>
@@ -3160,18 +3178,87 @@
         <v>162</v>
       </c>
       <c r="B88" t="s">
+        <v>153</v>
+      </c>
+      <c r="C88" t="s">
+        <v>154</v>
+      </c>
+      <c r="D88" t="s">
+        <v>223</v>
+      </c>
+      <c r="E88" t="s">
+        <v>219</v>
+      </c>
+      <c r="F88" t="s">
+        <v>11</v>
+      </c>
+      <c r="G88" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>162</v>
+      </c>
+      <c r="B89" t="s">
+        <v>155</v>
+      </c>
+      <c r="C89" t="s">
+        <v>156</v>
+      </c>
+      <c r="D89" t="s">
+        <v>224</v>
+      </c>
+      <c r="E89" t="s">
+        <v>220</v>
+      </c>
+      <c r="F89" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>162</v>
+      </c>
+      <c r="B90" t="s">
+        <v>157</v>
+      </c>
+      <c r="C90" t="s">
+        <v>158</v>
+      </c>
+      <c r="D90" t="s">
+        <v>225</v>
+      </c>
+      <c r="E90" t="s">
+        <v>221</v>
+      </c>
+      <c r="F90" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>162</v>
+      </c>
+      <c r="B91" t="s">
         <v>159</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D91" t="s">
         <v>160</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E91" t="s">
         <v>222</v>
       </c>
-      <c r="F88" t="s">
-        <v>11</v>
-      </c>
-      <c r="G88" t="s">
+      <c r="F91" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" t="s">
         <v>161</v>
       </c>
     </row>
